--- a/data/emissions_cost.xlsx
+++ b/data/emissions_cost.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oburdash\dev\repos\standard_inputs\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3461164D-BE18-4CB5-A6C0-A478BA128FD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7C693EC-4C47-4F64-8E1D-7E684DD60A4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="marginal" sheetId="1" r:id="rId1"/>
@@ -148,7 +148,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -181,7 +181,7 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
@@ -511,17 +511,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.85546875" customWidth="1"/>
-    <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.88671875" customWidth="1"/>
+    <col min="3" max="3" width="18.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>9</v>
       </c>
@@ -541,7 +541,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>500</v>
       </c>
@@ -552,16 +552,16 @@
         <v>2</v>
       </c>
       <c r="D2" s="2">
-        <v>130.64009975062342</v>
+        <v>134</v>
       </c>
       <c r="E2" s="3">
-        <v>0.36217057356608479</v>
+        <v>0.37</v>
       </c>
       <c r="F2" s="3">
-        <v>1.8367221945137155</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>500</v>
       </c>
@@ -572,16 +572,16 @@
         <v>4</v>
       </c>
       <c r="D3" s="2">
-        <v>177.20488778054863</v>
+        <v>182</v>
       </c>
       <c r="E3" s="3">
-        <v>0.38803990024937651</v>
+        <v>0.4</v>
       </c>
       <c r="F3" s="3">
-        <v>1.9660688279301746</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>2.0099999999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1500</v>
       </c>
@@ -592,16 +592,16 @@
         <v>5</v>
       </c>
       <c r="D4" s="2">
-        <v>213.42194513715708</v>
+        <v>219</v>
       </c>
       <c r="E4" s="3">
-        <v>9.0542643391521196E-2</v>
+        <v>0.09</v>
       </c>
       <c r="F4" s="3">
-        <v>1.4357476309226933</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1500</v>
       </c>
@@ -612,16 +612,16 @@
         <v>6</v>
       </c>
       <c r="D5" s="2">
-        <v>239.29127182044886</v>
+        <v>245</v>
       </c>
       <c r="E5" s="3">
-        <v>0.14228129675810472</v>
+        <v>0.15</v>
       </c>
       <c r="F5" s="3">
-        <v>2.04367680798005</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>2.09</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>3000</v>
       </c>
@@ -632,16 +632,16 @@
         <v>5</v>
       </c>
       <c r="D6" s="2">
-        <v>283.26912718204488</v>
+        <v>290</v>
       </c>
       <c r="E6" s="3">
-        <v>6.4673316708229428E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="F6" s="3">
-        <v>1.9013955112219449</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>3000</v>
       </c>
@@ -652,16 +652,16 @@
         <v>6</v>
       </c>
       <c r="D7" s="2">
-        <v>316.89925187032418</v>
+        <v>325</v>
       </c>
       <c r="E7" s="3">
-        <v>9.0542643391521196E-2</v>
+        <v>0.09</v>
       </c>
       <c r="F7" s="3">
-        <v>2.7033446384039896</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>2.77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>5000</v>
       </c>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="D8" s="2">
-        <v>649.3200997506234</v>
+        <v>665</v>
       </c>
       <c r="E8" s="3">
-        <v>3.8803990024937653E-2</v>
+        <v>0.04</v>
       </c>
       <c r="F8" s="3">
-        <v>2.1988927680798005</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>5000</v>
       </c>
@@ -692,16 +692,16 @@
         <v>8</v>
       </c>
       <c r="D9" s="2">
-        <v>1077.4574563591023</v>
+        <v>1104</v>
       </c>
       <c r="E9" s="3">
-        <v>5.1738653366583537E-2</v>
+        <v>0.05</v>
       </c>
       <c r="F9" s="3">
-        <v>2.4834553615960098</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>2.54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>15000</v>
       </c>
@@ -712,16 +712,16 @@
         <v>7</v>
       </c>
       <c r="D10" s="2">
-        <v>919.65456359102234</v>
+        <v>942</v>
       </c>
       <c r="E10" s="3">
-        <v>2.5869326683291768E-2</v>
+        <v>0.03</v>
       </c>
       <c r="F10" s="3">
-        <v>3.1172538653366582</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+        <v>3.19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>15000</v>
       </c>
@@ -732,13 +732,13 @@
         <v>8</v>
       </c>
       <c r="D11" s="2">
-        <v>1525</v>
+        <v>1563</v>
       </c>
       <c r="E11" s="3">
         <v>2.5869326683291768E-2</v>
       </c>
       <c r="F11" s="3">
-        <v>3.5182284289276806</v>
+        <v>3.6</v>
       </c>
     </row>
   </sheetData>
@@ -750,12 +750,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEB91990-7DAD-4E8B-9C7B-9A8D711A9792}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>16</v>
       </c>
@@ -769,32 +769,32 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" s="2">
-        <v>77.607980049875309</v>
+        <v>80</v>
       </c>
       <c r="C2" s="2">
-        <v>129.34663341645884</v>
+        <v>133</v>
       </c>
       <c r="D2" s="2">
-        <v>244.46513715710722</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>15</v>
       </c>
       <c r="B3" s="2">
-        <v>201.7807481296758</v>
+        <v>207</v>
       </c>
       <c r="C3" s="2">
-        <v>347.94244389027432</v>
+        <v>357</v>
       </c>
       <c r="D3" s="2">
-        <v>644.14623441396509</v>
+        <v>660</v>
       </c>
     </row>
   </sheetData>
@@ -805,14 +805,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E0B1D79-12F2-46D3-9AC6-97A92AB6DE61}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>9</v>
       </c>
@@ -826,46 +826,46 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>20</v>
       </c>
       <c r="B2" s="1">
-        <v>1.228793017456359</v>
+        <v>1.26</v>
       </c>
       <c r="C2" s="1">
-        <v>1.3710743142144639</v>
+        <v>1.4</v>
       </c>
       <c r="D2" s="2">
-        <v>754.09087281795507</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>21</v>
       </c>
       <c r="B3" s="1">
-        <v>2.7162793017456357</v>
+        <v>2.78</v>
       </c>
       <c r="C3" s="1">
-        <v>0.90542643391521183</v>
+        <v>0.93</v>
       </c>
       <c r="D3" s="2">
-        <v>1650.4630423940148</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1691</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>22</v>
       </c>
       <c r="B4" s="1">
-        <v>7.5409087281795504</v>
+        <v>7.73</v>
       </c>
       <c r="C4" s="1">
-        <v>1.1770543640897755</v>
+        <v>1.21</v>
       </c>
       <c r="D4" s="2">
-        <v>9249.5777556109715</v>
+        <v>9477</v>
       </c>
     </row>
   </sheetData>
@@ -876,9 +876,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A040B832-850D-4C40-9310-00058E91C5D7}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>26</v>
       </c>
@@ -895,21 +895,21 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>31</v>
       </c>
       <c r="B2" s="2">
-        <v>14.098783042394015</v>
+        <v>14.45</v>
       </c>
       <c r="C2" s="2">
-        <v>1.5521596009975061</v>
+        <v>1.59</v>
       </c>
       <c r="D2" s="2">
-        <v>14.098783042394015</v>
+        <v>14.45</v>
       </c>
       <c r="E2" s="2">
-        <v>25.093246882793014</v>
+        <v>25.71</v>
       </c>
     </row>
   </sheetData>
